--- a/stories/arbres/ATOM-FAM.AID.001-01.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Noé est dans sa chambre. Il veut le puzzle. La boîte est en haut. Trop haut. Noé lève les bras. Il n'arrive pas. Noé va vers la porte. Il va vers papa. Papa est dans le salon. Noé dit : papa. J'ai besoin de la boîte. Papa écoute. Papa vient. Papa donne la boîte. La boîte est lourde. Noé dit merci. On peut aller vers eux. On peut dire le besoin. On peut appeler papa ou maman. Papa sourit. Noé ouvre la boîte. Les pièces sont colorées.</t>
+          <t>Noé est dans sa chambre. Il veut le puzzle. La boîte est en haut. Trop haut. Noé lève les bras. Il n'arrive pas. Noé va vers la porte. Il va vers papa. Papa est dans le salon. Papa. J'ai besoin de la boîte. Papa écoute. Papa vient. Papa donne la boîte. La boîte est lourde. Noé dit merci. On peut aller vers eux. On peut dire le besoin. On peut appeler papa ou maman. Papa sourit. Noé ouvre la boîte. Les pièces sont colorées.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Noé est dans sa chambre. Il veut le puzzle. La boîte est en haut. Trop haut. Noé lève les bras. Il n'arrive pas. Noé va vers la porte. Il va vers papa. Papa est dans le salon.
+enfant-m|Papa. J'ai besoin de la boîte. Papa écoute. Papa vient. Papa donne la boîte.
+narrateur|La boîte est lourde. Noé dit merci. On peut aller vers eux. On peut dire le besoin. On peut appeler papa ou maman. Papa sourit. Noé ouvre la boîte. Les pièces sont colorées.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Noé n'arrive pas. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1629,6 +1657,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a appelé. Il a dit le besoin. Papa a entendu. La boîte est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1787,6 +1820,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose une pièce. Papa s'assoit près de lui. Le puzzle commence.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1949,6 +1987,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1967,7 +2010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1984,6 +2027,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.AID.001-01.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|La boîte est lourde. Noé dit merci. On peut aller vers eux. On peut dire le besoin. On peut appeler papa ou maman. Papa sourit. Noé ouvre la boîte. Les pièces sont colorées.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1501,7 @@
           <t>narrateur|Noé n'arrive pas. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1662,6 +1669,7 @@
           <t>narrateur|Noé a appelé. Il a dit le besoin. Papa a entendu. La boîte est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1833,7 @@
           <t>narrateur|Noé pose une pièce. Papa s'assoit près de lui. Le puzzle commence.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1992,6 +2001,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2010,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2034,6 +2044,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2048,7 +2072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2235,6 +2259,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-FAM.AID.001-01.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Noé appelle papa</t>
+          <t>La boîte trop haute</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La boîte du puzzle est trop haute. Chouchou va vers papa. Il dit le besoin. Papa donne la boîte.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Noé est dans sa chambre. Il veut le puzzle. La boîte est en haut. Trop haut. Noé lève les bras. Il n'arrive pas. Noé va vers la porte. Il va vers papa. Papa est dans le salon. Papa. J'ai besoin de la boîte. Papa écoute. Papa vient. Papa donne la boîte. La boîte est lourde. Noé dit merci. On peut aller vers eux. On peut dire le besoin. On peut appeler papa ou maman. Papa sourit. Noé ouvre la boîte. Les pièces sont colorées.</t>
+          <t>Le doudou attend sur l'oreiller. Il a une oreille un peu pliée. Un rayon de soleil traverse la chambre. Des poussières brillent dans le rayon. Sur l'étagère, une boîte colorée. La boîte a des pièces, dedans. Je suis dans la cuisine, Chouchou. Ça sent la soupe, déjà. Moi, je suis dans le salon. Le doudou est là. Il attend. En ce moment, Chouchou veut le puzzle. Il lève les yeux. La boîte est en haut. Trop haut. Je n'arrive pas. Chouchou baisse les bras. Il va vers la porte. Il va vers papa. Papa est dans le salon. Papa. J'ai besoin de la boîte. Je t'écoute, Chouchou. La boîte du puzzle, c'est ça ? Oui. Elle est trop haute. On va ensemble. Tu m'as appelé. Papa vient. Papa prend la boîte. Il la donne. La boîte est lourde. Merci, papa. On peut aller vers nous. On peut dire le besoin. On peut appeler papa ou maman. J'ai dit : j'ai besoin. Bravo, Chouchou. C'est du bon travail. Je t'entends, depuis la cuisine. Tu as appelé papa. Bravo. Tu ouvres la boîte, tout doux ? Oui. Les pièces sont colorées. Chouchou ouvre la boîte. Une pièce rouge. Une pièce bleue. Tu t'assieds près du tapis ? Oui. Le doudou peut regarder. Le doudou reste sur l'oreiller. La soupe est bientôt prête. On commence le puzzle, d'abord. J'ai appelé. Papa a entendu. Oui. Tu as dit le besoin. Le rayon de soleil a bougé. La boîte est là, sur le tapis.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,12 +1324,62 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Noé est dans sa chambre. Il veut le puzzle. La boîte est en haut. Trop haut. Noé lève les bras. Il n'arrive pas. Noé va vers la porte. Il va vers papa. Papa est dans le salon.
-enfant-m|Papa. J'ai besoin de la boîte. Papa écoute. Papa vient. Papa donne la boîte.
-narrateur|La boîte est lourde. Noé dit merci. On peut aller vers eux. On peut dire le besoin. On peut appeler papa ou maman. Papa sourit. Noé ouvre la boîte. Les pièces sont colorées.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le doudou attend sur l'oreiller.
+narrateur|Il a une oreille un peu pliée.
+narrateur|Un rayon de soleil traverse la chambre.
+narrateur|Des poussières brillent dans le rayon.
+narrateur|Sur l'étagère, une boîte colorée.
+narrateur|La boîte a des pièces, dedans.
+maman|Je suis dans la cuisine, Chouchou.
+maman|Ça sent la soupe, déjà.
+papa|Moi, je suis dans le salon.
+enfant-m|Le doudou est là. Il attend.
+narrateur|En ce moment, Chouchou veut le puzzle.
+narrateur|Il lève les yeux.
+narrateur|La boîte est en haut.
+narrateur|Trop haut.
+enfant-m|Je n'arrive pas.
+narrateur|Chouchou baisse les bras.
+narrateur|Il va vers la porte.
+narrateur|Il va vers papa.
+narrateur|Papa est dans le salon.
+enfant-m|Papa.
+enfant-m|J'ai besoin de la boîte.
+papa|Je t'écoute, Chouchou.
+papa|La boîte du puzzle, c'est ça ?
+enfant-m|Oui. Elle est trop haute.
+papa|On va ensemble. Tu m'as appelé.
+narrateur|Papa vient.
+narrateur|Papa prend la boîte. Il la donne.
+narrateur|La boîte est lourde.
+enfant-m|Merci, papa.
+papa|On peut aller vers nous.
+papa|On peut dire le besoin.
+papa|On peut appeler papa ou maman.
+enfant-m|J'ai dit : j'ai besoin.
+papa|Bravo, Chouchou. C'est du bon travail.
+maman|Je t'entends, depuis la cuisine.
+maman|Tu as appelé papa. Bravo.
+papa|Tu ouvres la boîte, tout doux ?
+enfant-m|Oui. Les pièces sont colorées.
+narrateur|Chouchou ouvre la boîte.
+narrateur|Une pièce rouge. Une pièce bleue.
+papa|Tu t'assieds près du tapis ?
+enfant-m|Oui. Le doudou peut regarder.
+papa|Le doudou reste sur l'oreiller.
+maman|La soupe est bientôt prête.
+papa|On commence le puzzle, d'abord.
+enfant-m|J'ai appelé. Papa a entendu.
+papa|Oui. Tu as dit le besoin.
+narrateur|Le rayon de soleil a bougé.
+narrateur|La boîte est là, sur le tapis.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>chambre,boite</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1342,7 +1404,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Noé n'arrive pas. Que fait-il ?</t>
+          <t>Chouchou n'arrive pas. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1498,7 +1560,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Noé n'arrive pas. Que fait-il ?</t>
+          <t>narrateur|Chouchou n'arrive pas.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1526,7 +1589,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Noé a appelé. Il a dit le besoin. Papa a entendu. La boîte est là.</t>
+          <t>Chouchou a appelé. Il a dit le besoin. Papa a entendu. La boîte est là. Papa. J'ai besoin de la boîte. Oui. Tu es venu vers moi. Bravo. C'est du bon travail. On peut appeler papa ou maman. J'ai dit le besoin. Tu veux commencer une pièce ? Oui. La rouge. La boîte reste sur le tapis.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1666,10 +1729,24 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Noé a appelé. Il a dit le besoin. Papa a entendu. La boîte est là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Chouchou a appelé.
+narrateur|Il a dit le besoin.
+narrateur|Papa a entendu. La boîte est là.
+enfant-m|Papa. J'ai besoin de la boîte.
+papa|Oui. Tu es venu vers moi.
+papa|Bravo. C'est du bon travail.
+maman|On peut appeler papa ou maman.
+enfant-m|J'ai dit le besoin.
+papa|Tu veux commencer une pièce ?
+enfant-m|Oui. La rouge.
+narrateur|La boîte reste sur le tapis.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>puzzle</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1694,7 +1771,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Noé pose une pièce. Papa s'assoit près de lui. Le puzzle commence.</t>
+          <t>Chouchou pose une pièce. Papa s'assoit près de lui. Le puzzle commence. Tu es prêt ? Oui. Merci, papa. Bravo, Chouchou. Tu as appelé. J'ai dit le besoin. C'est du bon travail. Le doudou attend encore sur l'oreiller. Une pièce rouge est déjà posée.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1830,10 +1907,22 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Noé pose une pièce. Papa s'assoit près de lui. Le puzzle commence.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Chouchou pose une pièce.
+narrateur|Papa s'assoit près de lui.
+papa|Le puzzle commence. Tu es prêt ?
+enfant-m|Oui. Merci, papa.
+maman|Bravo, Chouchou. Tu as appelé.
+enfant-m|J'ai dit le besoin.
+papa|C'est du bon travail.
+narrateur|Le doudou attend encore sur l'oreiller.
+narrateur|Une pièce rouge est déjà posée.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>puzzle</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1858,7 +1947,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai appelé papa. J'ai dit le besoin. Bravo. Tu as fait du bon travail. La boîte est là, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1998,7 +2087,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai appelé papa.
+enfant-m|J'ai dit le besoin.
+papa|Bravo. Tu as fait du bon travail.
+maman|La boîte est là, maintenant.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2020,7 +2113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2058,6 +2151,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.AID.001-01.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-01.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le doudou attend sur l'oreiller. Il a une oreille un peu pliée. Un rayon de soleil traverse la chambre. Des poussières brillent dans le rayon. Sur l'étagère, une boîte colorée. La boîte a des pièces, dedans. Je suis dans la cuisine, Chouchou. Ça sent la soupe, déjà. Moi, je suis dans le salon. Le doudou est là. Il attend. En ce moment, Chouchou veut le puzzle. Il lève les yeux. La boîte est en haut. Trop haut. Je n'arrive pas. Chouchou baisse les bras. Il va vers la porte. Il va vers papa. Papa est dans le salon. Papa. J'ai besoin de la boîte. Je t'écoute, Chouchou. La boîte du puzzle, c'est ça ? Oui. Elle est trop haute. On va ensemble. Tu m'as appelé. Papa vient. Papa prend la boîte. Il la donne. La boîte est lourde. Merci, papa. On peut aller vers nous. On peut dire le besoin. On peut appeler papa ou maman. J'ai dit : j'ai besoin. Bravo, Chouchou. C'est du bon travail. Je t'entends, depuis la cuisine. Tu as appelé papa. Bravo. Tu ouvres la boîte, tout doux ? Oui. Les pièces sont colorées. Chouchou ouvre la boîte. Une pièce rouge. Une pièce bleue. Tu t'assieds près du tapis ? Oui. Le doudou peut regarder. Le doudou reste sur l'oreiller. La soupe est bientôt prête. On commence le puzzle, d'abord. J'ai appelé. Papa a entendu. Oui. Tu as dit le besoin. Le rayon de soleil a bougé. La boîte est là, sur le tapis.</t>
+          <t>Le doudou attend sur l'oreiller. Il a une oreille un peu pliée. Un rayon de soleil traverse la chambre. Des poussières brillent dans le rayon. Sur l'étagère, une boîte colorée. La boîte a des pièces, dedans. Je suis dans la cuisine, Chouchou. Ça sent la soupe, déjà. Moi, je suis dans le salon. Le doudou est là. Il attend. En ce moment, Chouchou veut le puzzle. Il lève les yeux. La boîte est en haut. Trop haut. Je n'arrive pas. Chouchou baisse les bras. Il va vers la porte. Il va vers papa. Papa est dans le salon. Papa. J'ai besoin de la boîte. Je t'écoute, Chouchou. La boîte du puzzle, c'est ça ? Oui. Elle est trop haute. On va ensemble. Tu m'as appelé. Papa vient. Papa prend la boîte. Il la donne. La boîte est lourde. Merci, papa. On peut aller vers nous. On peut dire le besoin. On peut appeler papa ou maman. J'ai dit : j'ai besoin. Je t'entends, depuis la cuisine. Tu as appelé papa. Bravo. Tu ouvres la boîte, tout doux ? Oui. Les pièces sont colorées. Chouchou ouvre la boîte. Une pièce rouge. Une pièce bleue. Tu t'assieds près du tapis ? Oui. Le doudou peut regarder. Le doudou reste sur l'oreiller. La soupe est bientôt prête. On commence le puzzle, d'abord. J'ai appelé. Papa a entendu. Oui. Tu as dit le besoin. Le rayon de soleil a bougé. La boîte est là, sur le tapis.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Noé est dans sa chambre. Il veut le puzzle. La boîte est en haut. Trop haut. Noé lève les bras. Il n'arrive pas. Noé va vers la porte. Il va vers papa. Papa est dans le salon. Noé dit : papa. J'ai besoin de la boîte. Papa écoute. Papa vient. Papa donne la boîte. La boîte est lourde. Noé dit merci. On peut &lt;emphasis level="moderate"&gt;aller&lt;/emphasis&gt; vers eux. On peut dire le besoin. On peut appeler papa ou maman. Papa sourit. Noé ouvre la boîte. Les pièces sont colorées.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le doudou attend sur l'oreiller. Il a une oreille un peu pliée. Un rayon de soleil traverse la chambre. Des poussières brillent dans le rayon. Sur l'étagère, une boîte colorée. La boîte a des pièces, dedans. Je suis dans la cuisine, Chouchou. Ça sent la soupe, déjà. Moi, je suis dans le salon. Le doudou est là. Il attend. En ce moment, Chouchou veut le puzzle. Il lève les yeux. La boîte est en haut. Trop haut. Je n'arrive pas. Chouchou baisse les bras. Il va vers la porte. Il va vers papa. Papa est dans le salon. Papa. J'ai besoin de la boîte. Je t'écoute, Chouchou. La boîte du puzzle, c'est ça ? Oui. Elle est trop haute. On va ensemble. Tu m'as appelé. Papa vient. Papa prend la boîte. Il la donne. La boîte est lourde. Merci, papa. On peut aller vers nous. On peut dire le besoin. On peut appeler papa ou maman. J'ai dit : j'ai besoin. Je t'entends, depuis la cuisine. Tu as appelé papa. Bravo. Tu ouvres la boîte, tout doux ? Oui. Les pièces sont colorées. Chouchou ouvre la boîte. Une pièce rouge. Une pièce bleue. Tu t'assieds près du tapis ? Oui. Le doudou peut regarder. Le doudou reste sur l'oreiller. La soupe est bientôt prête. On commence le puzzle, d'abord. J'ai appelé. Papa a entendu. Oui. Tu as dit le besoin. Le rayon de soleil a bougé. La boîte est là, sur le tapis.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1357,7 +1357,6 @@
 papa|On peut dire le besoin.
 papa|On peut appeler papa ou maman.
 enfant-m|J'ai dit : j'ai besoin.
-papa|Bravo, Chouchou. C'est du bon travail.
 maman|Je t'entends, depuis la cuisine.
 maman|Tu as appelé papa. Bravo.
 papa|Tu ouvres la boîte, tout doux ?
@@ -1409,7 +1408,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Noé n'arrive pas. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou n'arrive pas. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1564,7 +1563,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1589,12 +1587,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Chouchou a appelé. Il a dit le besoin. Papa a entendu. La boîte est là. Papa. J'ai besoin de la boîte. Oui. Tu es venu vers moi. Bravo. C'est du bon travail. On peut appeler papa ou maman. J'ai dit le besoin. Tu veux commencer une pièce ? Oui. La rouge. La boîte reste sur le tapis.</t>
+          <t>Chouchou a appelé. Il a dit le besoin. Papa a entendu. La boîte est là. Papa. J'ai besoin de la boîte. Oui. Tu es venu vers moi. On peut appeler papa ou maman. J'ai dit le besoin. Tu veux commencer une pièce ? Oui. La rouge. La boîte reste sur le tapis.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Noé a appelé. Il a dit le besoin. Papa a entendu. La boîte est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou a appelé. Il a dit le besoin. Papa a entendu. La boîte est là. Papa. J'ai besoin de la boîte. Oui. Tu es venu vers moi. On peut appeler papa ou maman. J'ai dit le besoin. Tu veux commencer une pièce ? Oui. La rouge. La boîte reste sur le tapis.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1734,7 +1732,6 @@
 narrateur|Papa a entendu. La boîte est là.
 enfant-m|Papa. J'ai besoin de la boîte.
 papa|Oui. Tu es venu vers moi.
-papa|Bravo. C'est du bon travail.
 maman|On peut appeler papa ou maman.
 enfant-m|J'ai dit le besoin.
 papa|Tu veux commencer une pièce ?
@@ -1771,12 +1768,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Chouchou pose une pièce. Papa s'assoit près de lui. Le puzzle commence. Tu es prêt ? Oui. Merci, papa. Bravo, Chouchou. Tu as appelé. J'ai dit le besoin. C'est du bon travail. Le doudou attend encore sur l'oreiller. Une pièce rouge est déjà posée.</t>
+          <t>Chouchou pose une pièce. Papa s'assoit près de lui. Le puzzle commence. Tu es prêt ? Oui. Merci, papa. Bravo, Chouchou. Tu as appelé. J'ai dit le besoin. Le doudou attend encore sur l'oreiller. Une pièce rouge est déjà posée.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Noé pose une pièce. Papa s'assoit près de lui. Le puzzle commence.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou pose une pièce. Papa s'assoit près de lui. Le puzzle commence. Tu es prêt ? Oui. Merci, papa. Bravo, Chouchou. Tu as appelé. J'ai dit le besoin. Le doudou attend encore sur l'oreiller. Une pièce rouge est déjà posée.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1913,7 +1910,6 @@
 enfant-m|Oui. Merci, papa.
 maman|Bravo, Chouchou. Tu as appelé.
 enfant-m|J'ai dit le besoin.
-papa|C'est du bon travail.
 narrateur|Le doudou attend encore sur l'oreiller.
 narrateur|Une pièce rouge est déjà posée.</t>
         </is>
@@ -1947,12 +1943,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai appelé papa. J'ai dit le besoin. Bravo. Tu as fait du bon travail. La boîte est là, maintenant. L'histoire est finie.</t>
+          <t>J'ai appelé papa. J'ai dit le besoin. La boîte est là, maintenant.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai appelé papa. J'ai dit le besoin. La boîte est là, maintenant.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2089,12 +2085,9 @@
         <is>
           <t>enfant-m|J'ai appelé papa.
 enfant-m|J'ai dit le besoin.
-papa|Bravo. Tu as fait du bon travail.
-maman|La boîte est là, maintenant.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|La boîte est là, maintenant.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2113,7 +2106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2158,6 +2151,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.AID.001-01.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-01.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Noé, papa, maman</t>
+          <t>Chouchou, papa, maman</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.AID.001-01.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-01.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>chambre</t>
+          <t>chambre, puis tapis</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>La boîte du puzzle est trop haute. Chouchou va vers papa. Il dit le besoin. Papa donne la boîte.</t>
+          <t>Chouchou veut le bateau du puzzle. La boîte est trop haute. Elle va vers papa. Ensemble ils finissent le bateau.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le doudou attend sur l'oreiller. Il a une oreille un peu pliée. Un rayon de soleil traverse la chambre. Des poussières brillent dans le rayon. Sur l'étagère, une boîte colorée. La boîte a des pièces, dedans. Je suis dans la cuisine, Chouchou. Ça sent la soupe, déjà. Moi, je suis dans le salon. Le doudou est là. Il attend. En ce moment, Chouchou veut le puzzle. Il lève les yeux. La boîte est en haut. Trop haut. Je n'arrive pas. Chouchou baisse les bras. Il va vers la porte. Il va vers papa. Papa est dans le salon. Papa. J'ai besoin de la boîte. Je t'écoute, Chouchou. La boîte du puzzle, c'est ça ? Oui. Elle est trop haute. On va ensemble. Tu m'as appelé. Papa vient. Papa prend la boîte. Il la donne. La boîte est lourde. Merci, papa. On peut aller vers nous. On peut dire le besoin. On peut appeler papa ou maman. J'ai dit : j'ai besoin. Je t'entends, depuis la cuisine. Tu as appelé papa. Bravo. Tu ouvres la boîte, tout doux ? Oui. Les pièces sont colorées. Chouchou ouvre la boîte. Une pièce rouge. Une pièce bleue. Tu t'assieds près du tapis ? Oui. Le doudou peut regarder. Le doudou reste sur l'oreiller. La soupe est bientôt prête. On commence le puzzle, d'abord. J'ai appelé. Papa a entendu. Oui. Tu as dit le besoin. Le rayon de soleil a bougé. La boîte est là, sur le tapis.</t>
+          <t>Le doudou attend sur l'oreiller. Il a une oreille un peu pliée. Un rayon traverse la chambre. Des poussières brillent dans le rayon. Sur l'étagère, une boîte colorée. Dedans, il y a le bateau du puzzle. Je suis dans la cuisine, Chouchou. Ça sent la soupe, déjà. Moi, je suis dans le salon. Le doudou attend le bateau. En ce moment, Chouchou veut le puzzle. Elle lève les yeux. La boîte est en haut. Trop haut. Je n'arrive pas. Elle baisse les bras. Elle va vers la porte. Elle va vers papa. Papa. La boîte est trop haute. Je t'écoute, Chouchou. Le bateau du puzzle, c'est ça ? Oui. Papa se lève. Il prend la boîte, tout doux. Elle est lourde. Merci, papa. Merci d'être venue me voir. Ils reviennent près du tapis. Le doudou garde l'oreiller. Tu ouvres, tout doux ? Oui. Une pièce rouge. Une pièce bleue. Un coin de voile blanche. Une pièce sent le carton. Celle-ci, c'est la coque. Et ça, la petite cheminée ? Oui. La soupe attend encore un peu. On finit le bateau, d'abord ?</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Le doudou attend sur l'oreiller. Il a une oreille un peu pliée. Un rayon de soleil traverse la chambre. Des poussières brillent dans le rayon. Sur l'étagère, une boîte colorée. La boîte a des pièces, dedans. Je suis dans la cuisine, Chouchou. Ça sent la soupe, déjà. Moi, je suis dans le salon. Le doudou est là. Il attend. En ce moment, Chouchou veut le puzzle. Il lève les yeux. La boîte est en haut. Trop haut. Je n'arrive pas. Chouchou baisse les bras. Il va vers la porte. Il va vers papa. Papa est dans le salon. Papa. J'ai besoin de la boîte. Je t'écoute, Chouchou. La boîte du puzzle, c'est ça ? Oui. Elle est trop haute. On va ensemble. Tu m'as appelé. Papa vient. Papa prend la boîte. Il la donne. La boîte est lourde. Merci, papa. On peut aller vers nous. On peut dire le besoin. On peut appeler papa ou maman. J'ai dit : j'ai besoin. Je t'entends, depuis la cuisine. Tu as appelé papa. Bravo. Tu ouvres la boîte, tout doux ? Oui. Les pièces sont colorées. Chouchou ouvre la boîte. Une pièce rouge. Une pièce bleue. Tu t'assieds près du tapis ? Oui. Le doudou peut regarder. Le doudou reste sur l'oreiller. La soupe est bientôt prête. On commence le puzzle, d'abord. J'ai appelé. Papa a entendu. Oui. Tu as dit le besoin. Le rayon de soleil a bougé. La boîte est là, sur le tapis.</t>
+          <t>Le doudou attend sur l'oreiller. Il a une oreille un peu pliée. Un rayon traverse la chambre. Des poussières brillent dans le rayon. Sur l'étagère, une boîte colorée. Dedans, il y a le bateau du puzzle. Je suis dans la cuisine, Chouchou. Ça sent la soupe, déjà. Moi, je suis dans le salon. Le doudou attend le bateau. En ce moment, Chouchou veut le puzzle. Elle lève les yeux. La boîte est en haut. Trop haut. Je n'arrive pas. Elle baisse les bras. Elle va vers la porte. Elle va vers papa. Papa. La boîte est trop haute. Je t'écoute, Chouchou. Le bateau du puzzle, c'est ça ? Oui. Papa se lève. Il prend la boîte, tout doux. Elle est lourde. Merci, papa. Merci d'être venue me voir. Ils reviennent près du tapis. Le doudou garde l'oreiller. Tu ouvres, tout doux ? Oui. Une pièce rouge. Une pièce bleue. Un coin de voile blanche. Une pièce sent le carton. Celle-ci, c'est la coque. Et ça, la petite cheminée ? Oui. La soupe attend encore un peu. On finit le bateau, d'abord ?</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1245,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1326,57 +1326,50 @@
         <is>
           <t>narrateur|Le doudou attend sur l'oreiller.
 narrateur|Il a une oreille un peu pliée.
-narrateur|Un rayon de soleil traverse la chambre.
+narrateur|Un rayon traverse la chambre.
 narrateur|Des poussières brillent dans le rayon.
 narrateur|Sur l'étagère, une boîte colorée.
-narrateur|La boîte a des pièces, dedans.
+narrateur|Dedans, il y a le bateau du puzzle.
 maman|Je suis dans la cuisine, Chouchou.
 maman|Ça sent la soupe, déjà.
 papa|Moi, je suis dans le salon.
-enfant-m|Le doudou est là. Il attend.
+enfant-f|Le doudou attend le bateau.
 narrateur|En ce moment, Chouchou veut le puzzle.
-narrateur|Il lève les yeux.
+narrateur|Elle lève les yeux.
 narrateur|La boîte est en haut.
 narrateur|Trop haut.
-enfant-m|Je n'arrive pas.
-narrateur|Chouchou baisse les bras.
-narrateur|Il va vers la porte.
-narrateur|Il va vers papa.
-narrateur|Papa est dans le salon.
-enfant-m|Papa.
-enfant-m|J'ai besoin de la boîte.
+enfant-f|Je n'arrive pas.
+narrateur|Elle baisse les bras.
+narrateur|Elle va vers la porte.
+narrateur|Elle va vers papa.
+enfant-f|Papa.
+enfant-f|La boîte est trop haute.
 papa|Je t'écoute, Chouchou.
-papa|La boîte du puzzle, c'est ça ?
-enfant-m|Oui. Elle est trop haute.
-papa|On va ensemble. Tu m'as appelé.
-narrateur|Papa vient.
-narrateur|Papa prend la boîte. Il la donne.
-narrateur|La boîte est lourde.
-enfant-m|Merci, papa.
-papa|On peut aller vers nous.
-papa|On peut dire le besoin.
-papa|On peut appeler papa ou maman.
-enfant-m|J'ai dit : j'ai besoin.
-maman|Je t'entends, depuis la cuisine.
-maman|Tu as appelé papa. Bravo.
-papa|Tu ouvres la boîte, tout doux ?
-enfant-m|Oui. Les pièces sont colorées.
-narrateur|Chouchou ouvre la boîte.
-narrateur|Une pièce rouge. Une pièce bleue.
-papa|Tu t'assieds près du tapis ?
-enfant-m|Oui. Le doudou peut regarder.
-papa|Le doudou reste sur l'oreiller.
-maman|La soupe est bientôt prête.
-papa|On commence le puzzle, d'abord.
-enfant-m|J'ai appelé. Papa a entendu.
-papa|Oui. Tu as dit le besoin.
-narrateur|Le rayon de soleil a bougé.
-narrateur|La boîte est là, sur le tapis.</t>
+papa|Le bateau du puzzle, c'est ça ?
+enfant-f|Oui.
+narrateur|Papa se lève.
+narrateur|Il prend la boîte, tout doux.
+narrateur|Elle est lourde.
+enfant-f|Merci, papa.
+papa|Merci d'être venue me voir.
+narrateur|Ils reviennent près du tapis.
+narrateur|Le doudou garde l'oreiller.
+papa|Tu ouvres, tout doux ?
+enfant-f|Oui.
+narrateur|Une pièce rouge.
+narrateur|Une pièce bleue.
+narrateur|Un coin de voile blanche.
+narrateur|Une pièce sent le carton.
+enfant-f|Celle-ci, c'est la coque.
+papa|Et ça, la petite cheminée ?
+enfant-f|Oui.
+maman|La soupe attend encore un peu.
+papa|On finit le bateau, d'abord ?</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>chambre,boite</t>
+          <t>boite</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1396,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Chouchou n'arrive pas. Que fait-il ?</t>
+          <t>La boîte est trop haute. Que fait Chouchou ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Chouchou n'arrive pas. Que fait-il ?</t>
+          <t>La boîte est trop haute. Que fait Chouchou ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1418,12 +1411,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>appeler</t>
+          <t>papa</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>appeler | papa | maman | dire</t>
+          <t>papa | maman | appeler | elle va vers papa | dire</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1438,7 +1431,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il va vers papa. Il dit le besoin. Que fait Noé ?</t>
+          <t>La boîte est trop haute. Que fait Chouchou ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1487,7 +1480,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1559,8 +1552,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Chouchou n'arrive pas.
-narrateur|Que fait-il ?</t>
+          <t>narrateur|La boîte est trop haute.
+maman|Que fait Chouchou ?</t>
         </is>
       </c>
     </row>
@@ -1587,12 +1580,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Chouchou a appelé. Il a dit le besoin. Papa a entendu. La boîte est là. Papa. J'ai besoin de la boîte. Oui. Tu es venu vers moi. On peut appeler papa ou maman. J'ai dit le besoin. Tu veux commencer une pièce ? Oui. La rouge. La boîte reste sur le tapis.</t>
+          <t>Chouchou s'assoit près du tapis. Papa s'assoit aussi. La rouge, d'abord. La pièce clique sur le carton. Une autre pièce manque encore. Elle est sous la boîte. Tu la prends ? Chouchou glisse la main dessous. La pièce bleue revient. Et la voile ? Elle est un peu pliée. On la lisse du doigt ? Chouchou lisse le papier. La voile se tient.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Chouchou a appelé. Il a dit le besoin. Papa a entendu. La boîte est là. Papa. J'ai besoin de la boîte. Oui. Tu es venu vers moi. On peut appeler papa ou maman. J'ai dit le besoin. Tu veux commencer une pièce ? Oui. La rouge. La boîte reste sur le tapis.</t>
+          <t>Chouchou s'assoit près du tapis. Papa s'assoit aussi. La rouge, d'abord. La pièce clique sur le carton. Une autre pièce manque encore. Elle est sous la boîte. Tu la prends ? Chouchou glisse la main dessous. La pièce bleue revient. Et la voile ? Elle est un peu pliée. On la lisse du doigt ? Chouchou lisse le papier. La voile se tient.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1648,14 +1641,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1727,21 +1720,25 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Chouchou a appelé.
-narrateur|Il a dit le besoin.
-narrateur|Papa a entendu. La boîte est là.
-enfant-m|Papa. J'ai besoin de la boîte.
-papa|Oui. Tu es venu vers moi.
-maman|On peut appeler papa ou maman.
-enfant-m|J'ai dit le besoin.
-papa|Tu veux commencer une pièce ?
-enfant-m|Oui. La rouge.
-narrateur|La boîte reste sur le tapis.</t>
+          <t>narrateur|Chouchou s'assoit près du tapis.
+narrateur|Papa s'assoit aussi.
+enfant-f|La rouge, d'abord.
+narrateur|La pièce clique sur le carton.
+narrateur|Une autre pièce manque encore.
+enfant-f|Elle est sous la boîte.
+papa|Tu la prends ?
+narrateur|Chouchou glisse la main dessous.
+narrateur|La pièce bleue revient.
+papa|Et la voile ?
+enfant-f|Elle est un peu pliée.
+papa|On la lisse du doigt ?
+narrateur|Chouchou lisse le papier.
+narrateur|La voile se tient.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>puzzle</t>
+          <t>piece</t>
         </is>
       </c>
     </row>
@@ -1768,12 +1765,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Chouchou pose une pièce. Papa s'assoit près de lui. Le puzzle commence. Tu es prêt ? Oui. Merci, papa. Bravo, Chouchou. Tu as appelé. J'ai dit le besoin. Le doudou attend encore sur l'oreiller. Une pièce rouge est déjà posée.</t>
+          <t>Le bateau a une coque rouge. La voile est blanche, un peu froissée. Il peut partir. Souffle, tout doux. Chouchou souffle. La voile bouge. Il avance. Jusqu'à l'oreiller ? Jusqu'au doudou. Le bateau s'arrête contre le doudou. Je vous entends, depuis la cuisine. Le doudou a l'oreille moins pliée.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Chouchou pose une pièce. Papa s'assoit près de lui. Le puzzle commence. Tu es prêt ? Oui. Merci, papa. Bravo, Chouchou. Tu as appelé. J'ai dit le besoin. Le doudou attend encore sur l'oreiller. Une pièce rouge est déjà posée.</t>
+          <t>Le bateau a une coque rouge. La voile est blanche, un peu froissée. Il peut partir. Souffle, tout doux. Chouchou souffle. La voile bouge. Il avance. Jusqu'à l'oreiller ? Jusqu'au doudou. Le bateau s'arrête contre le doudou. Je vous entends, depuis la cuisine. Le doudou a l'oreille moins pliée.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1829,14 +1826,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1904,14 +1901,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Chouchou pose une pièce.
-narrateur|Papa s'assoit près de lui.
-papa|Le puzzle commence. Tu es prêt ?
-enfant-m|Oui. Merci, papa.
-maman|Bravo, Chouchou. Tu as appelé.
-enfant-m|J'ai dit le besoin.
-narrateur|Le doudou attend encore sur l'oreiller.
-narrateur|Une pièce rouge est déjà posée.</t>
+          <t>narrateur|Le bateau a une coque rouge.
+narrateur|La voile est blanche, un peu froissée.
+enfant-f|Il peut partir.
+papa|Souffle, tout doux.
+narrateur|Chouchou souffle.
+narrateur|La voile bouge.
+enfant-f|Il avance.
+papa|Jusqu'à l'oreiller ?
+enfant-f|Jusqu'au doudou.
+narrateur|Le bateau s'arrête contre le doudou.
+maman|Je vous entends, depuis la cuisine.
+narrateur|Le doudou a l'oreille moins pliée.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1943,12 +1944,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai appelé papa. J'ai dit le besoin. La boîte est là, maintenant.</t>
+          <t>Le bateau reste sur le tapis. La boîte est vide, à côté. Le doudou a vu le voyage. On range les pièces plus tard. La soupe est prête, maintenant. Le rayon a bougé sur l'oreiller. Le bateau attend encore. On le laisse pour ce soir. La boîte reste ouverte, tout près. Ça sent encore la soupe, dans l'escalier.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>J'ai appelé papa. J'ai dit le besoin. La boîte est là, maintenant.</t>
+          <t>Le bateau reste sur le tapis. La boîte est vide, à côté. Le doudou a vu le voyage. On range les pièces plus tard. La soupe est prête, maintenant. Le rayon a bougé sur l'oreiller. Le bateau attend encore. On le laisse pour ce soir. La boîte reste ouverte, tout près. Ça sent encore la soupe, dans l'escalier.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2004,14 +2005,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2083,9 +2084,16 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-m|J'ai appelé papa.
-enfant-m|J'ai dit le besoin.
-maman|La boîte est là, maintenant.</t>
+          <t>narrateur|Le bateau reste sur le tapis.
+narrateur|La boîte est vide, à côté.
+enfant-f|Le doudou a vu le voyage.
+papa|On range les pièces plus tard.
+maman|La soupe est prête, maintenant.
+narrateur|Le rayon a bougé sur l'oreiller.
+enfant-f|Le bateau attend encore.
+papa|On le laisse pour ce soir.
+narrateur|La boîte reste ouverte, tout près.
+narrateur|Ça sent encore la soupe, dans l'escalier.</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2156,6 +2164,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
